--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
@@ -4,17 +4,40 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9420"/>
+    <workbookView windowWidth="19455" windowHeight="7710"/>
   </bookViews>
   <sheets>
-    <sheet name="产品计划排期信息" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t>产品主代码*</t>
+  </si>
+  <si>
+    <t>开放期起始日*</t>
+  </si>
+  <si>
+    <t>开放期结束日（YYYY-MM-DD)*</t>
+  </si>
+  <si>
+    <t>产品冷静期（YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>运作起始日（YYYY-MM-DD)*</t>
+  </si>
+  <si>
+    <t>自动赎回日（YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>客户实际持有天数</t>
+  </si>
   <si>
     <t>产品名称</t>
   </si>
@@ -28,38 +51,21 @@
     <t>开放结束日</t>
   </si>
   <si>
-    <t>产品冷静期</t>
-  </si>
-  <si>
     <t>运作起始日</t>
   </si>
   <si>
     <t>自动赎回日</t>
-  </si>
-  <si>
-    <t>实际持有天数</t>
-  </si>
-  <si>
-    <t>数据状态</t>
-  </si>
-  <si>
-    <t>更新时间</t>
-  </si>
-  <si>
-    <t>更新人</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="0.00000_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -70,12 +76,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -231,7 +235,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,7 +549,9 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -691,47 +697,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -784,7 +756,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1080,345 +1052,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="41.8888888888889" style="2" customWidth="1"/>
-    <col min="2" max="4" width="20.7777777777778" style="2" customWidth="1"/>
-    <col min="5" max="6" width="20.7777777777778" style="3" customWidth="1"/>
-    <col min="7" max="9" width="20.7777777777778" style="4" customWidth="1"/>
-    <col min="10" max="10" width="20.7777777777778" style="5" customWidth="1"/>
-    <col min="11" max="11" width="16.5" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.5416666666667" customWidth="1"/>
+    <col min="2" max="2" width="16.0916666666667" customWidth="1"/>
+    <col min="3" max="3" width="26.725" customWidth="1"/>
+    <col min="4" max="4" width="27.8166666666667" customWidth="1"/>
+    <col min="5" max="5" width="24.9083333333333" customWidth="1"/>
+    <col min="6" max="6" width="23.45" customWidth="1"/>
+    <col min="7" max="7" width="14.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="13" customHeight="1" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:A8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="12.3666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19455" windowHeight="7710"/>
+    <workbookView windowWidth="23040" windowHeight="9420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>产品主代码*</t>
   </si>
@@ -37,24 +37,6 @@
   </si>
   <si>
     <t>客户实际持有天数</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>产品主代码</t>
-  </si>
-  <si>
-    <t>开放起始日</t>
-  </si>
-  <si>
-    <t>开放结束日</t>
-  </si>
-  <si>
-    <t>运作起始日</t>
-  </si>
-  <si>
-    <t>自动赎回日</t>
   </si>
 </sst>
 </file>
@@ -697,11 +679,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1053,37 +1041,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.5416666666667" customWidth="1"/>
-    <col min="2" max="2" width="16.0916666666667" customWidth="1"/>
-    <col min="3" max="3" width="26.725" customWidth="1"/>
-    <col min="4" max="4" width="27.8166666666667" customWidth="1"/>
-    <col min="5" max="5" width="24.9083333333333" customWidth="1"/>
-    <col min="6" max="6" width="23.45" customWidth="1"/>
-    <col min="7" max="7" width="14.6333333333333" customWidth="1"/>
+    <col min="1" max="1" width="11.5462962962963" customWidth="1"/>
+    <col min="2" max="2" width="16.0925925925926" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.8148148148148" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.9074074074074" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.4537037037037" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1097,48 +1085,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:A8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.3666666666667" customWidth="1"/>
+    <col min="1" max="1" width="12.3703703703704" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1149,7 +1101,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
@@ -21,33 +21,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>产品主代码*</t>
-  </si>
-  <si>
-    <t>开放期起始日*</t>
-  </si>
-  <si>
-    <t>开放期结束日（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>产品冷静期（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>运作起始日（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>自动赎回日（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>客户实际持有天数</t>
-  </si>
-  <si>
-    <t>产品名称*</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品主代码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开放起始日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开放结束日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品冷静期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>运作起始日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动赎回日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际持有天数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -436,46 +452,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="16.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.08984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="18.08984375" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/DisProdPlanManage001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\idea\ny\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,10 +27,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>产品主代码</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -64,6 +60,10 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -453,54 +453,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.08984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="13.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="18.125" customWidth="1"/>
+    <col min="11" max="11" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -513,9 +513,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -527,7 +527,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
